--- a/data/qa/prospect_to_cash/customer_order_line.xlsx
+++ b/data/qa/prospect_to_cash/customer_order_line.xlsx
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,126 +426,126 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:X11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>qa_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>domain</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>module</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>field</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>intent</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>sub_intent</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>canonical_question</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>answer</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>keywords</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>synonyms</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>route</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>source_reference</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>source_section</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>site_scope</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>security_scope</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>approval_status</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>approved_by</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>effective_date</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>last_reviewed_date</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
@@ -542,7 +554,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>QA-0014</t>
+          <t>KB-0042</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -552,54 +564,38 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Customer Order</t>
+          <t>Customer Order Line and Release Module</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Order Entry</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Customer Orders</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Order Line</t>
-        </is>
-      </c>
+          <t>Customer Order Line and Release Module</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>HELP_FIELD</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>definition</t>
-        </is>
-      </c>
+          <t>HELP_GENERIC</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>What is an Order Line?</t>
+          <t>What is a Customer Order Line and how does it relate to the order header?</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>An Order Line is a single item or service entry within a Customer Order, specifying the item, quantity, price, and due date for that particular line.</t>
+          <t>A Customer Order Line describes an item or service sold under a Customer Orders header. Lines and blanket releases carry their own item, quantity, unit, price, due date, source, site, and fulfillment state. The header's status does not replace the line status.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>order line,line item</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>line item,order item</t>
-        </is>
-      </c>
+          <t>customer order line, order header, line status, item, quantity</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>FAST_QA</t>
@@ -607,18 +603,16 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>PTC Training Guide</t>
+          <t>customer_order_line.md</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>4.3</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+          <t>Customer Order Line and Release Module &gt; Meaning and relationship to header</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -631,10 +625,14 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V2" t="b">
@@ -642,10 +640,892 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KB-0043</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Customer Order Line and Release Module</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Customer Order Line and Release Module</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>HELP_GENERIC</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Can a blanket line have multiple releases with different ship dates?</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>A blanket line can have multiple releases, each with its own scheduled ship date.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blanket release, blanket line, scheduled ship date, line release</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>customer_order_line.md</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Customer Order Line and Release Module &gt; Meaning and relationship to header</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KB-0044</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Customer Order Line and Release Module</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Customer Order Line and Release Module</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>How do I enter and validate a customer order line?</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Open the correct Customer Orders header and select Lines. Enter or select the line number and item, confirm the description and intended shipping site, enter Qty Ordered, and verify U/M, unit price, line discount, tax treatment, and due date. Review the source or cross-reference for supply, and check reservation, lot/serial, configuration, drop-ship, and invoice-hold options if needed. Save and check the resulting line status, warnings, credit hold, totals, and available-to-ship information.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>order line, Qty Ordered, U/M, due date, item</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>customer_order_line.md</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Customer Order Line and Release Module &gt; Enter and validate a line</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V4" t="b">
+        <v>1</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KB-0045</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Customer Order Line and Release Module</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Customer Order Line and Release Module</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>What should I review after saving a customer order line?</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>After saving a line, check the resulting line status, warnings, credit hold, totals, and available-to-ship information. Also review credit, sourcing, availability, and pricing.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>line status, credit hold, totals, available-to-ship</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>customer_order_line.md</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Customer Order Line and Release Module &gt; Enter and validate a line</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V5" t="b">
+        <v>1</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KB-0046</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Customer Order Line and Release Module</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Customer Order Line and Release Module</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>HELP_GENERIC</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>What happens to a customer order line if Allow Over Credit Limit is off?</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>An over-limit line remains Planned when Allow Over Credit Limit is off; other settings can place an order on credit hold.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Planned line, Ordered line, Allow Over Credit Limit, credit hold</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>customer_order_line.md</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Customer Order Line and Release Module &gt; Planned, Ordered, and credit checks</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V6" t="b">
+        <v>1</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KB-0047</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Customer Order Line and Release Module</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Customer Order Line and Release Module</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>How can I change a customer order line from Planned to Ordered?</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>The Change CO Line/Release Status Utility can move selected lines/releases from Planned to Ordered and performs credit checks. Only an authorized operator should perform that change.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Change CO Line/Release Status, Planned line, Ordered line, credit checks</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>customer_order_line.md</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Customer Order Line and Release Module &gt; Planned, Ordered, and credit checks</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V7" t="b">
+        <v>1</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KB-0048</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Customer Order Line and Release Module</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Customer Order Line and Release Module</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HELP_GENERIC</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Why might the Available to Ship Report show a different quantity than the line's Ready quantity?</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>The Available to Ship Report may differ from the line's Ready quantity because it considers competing order demand while processing.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>available to ship, ready quantity, report, competing order demand</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>customer_order_line.md</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Customer Order Line and Release Module &gt; Availability, partials, and cross-references</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V8" t="b">
+        <v>1</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KB-0049</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Customer Order Line and Release Module</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Customer Order Line and Release Module</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>What should I check before promising product availability to a customer?</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Before promising availability, check the shipping site's inventory, due date, reservations, source cross-reference, and shipped quantity.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>availability, inventory, due date, reservations, cross-reference</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>customer_order_line.md</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Customer Order Line and Release Module &gt; Availability, partials, and cross-references</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V9" t="b">
+        <v>1</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>KB-0050</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Customer Order Line and Release Module</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Customer Order Line and Release Module</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>What happens if I change the quantity on a customer order line?</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Changing line quantity does not always refresh Unit Price automatically. Confirm whether the current price should remain or be recalculated under the customer's agreement and the site's pricing rules.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>line quantity, Unit Price, price change, pricing rules</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>customer_order_line.md</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Customer Order Line and Release Module &gt; Price changes and invoice hold</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V10" t="b">
+        <v>1</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>KB-0051</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Customer Order Line and Release Module</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Customer Order Line and Release Module</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>How does Invoice Hold affect invoicing shipped lines?</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Invoice Hold can keep an otherwise shipped line from being invoiced. A shipped or invoiced line requires a controlled correction path; do not promise that it can be freely deleted or edited.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Invoice Hold, shipped line, invoicing, edit shipped line</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>customer_order_line.md</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Customer Order Line and Release Module &gt; Price changes and invoice hold</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V11" t="b">
+        <v>1</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -662,39 +1542,939 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>qa_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>variation_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>question_variation</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>validated</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>KB-0042</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>How do order lines work with the order header?</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KB-0042</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>What's the relationship between a customer order line and the header?</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KB-0042</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Explain what a customer order line is.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KB-0043</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Do blanket lines support several releases?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KB-0043</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Can I set different ship dates for releases on a blanket line?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KB-0043</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Are multiple releases possible on a blanket line?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KB-0044</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>What are the steps to add and check a customer order line?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KB-0044</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>How do I fill out and review a line on a customer order?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>KB-0044</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>What's the process for entering and validating an order line?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>KB-0045</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>What do I need to check once I've saved an order line?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>KB-0045</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>After saving a line, what should I look at?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>KB-0045</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>What reviews are needed post-saving a customer order line?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>KB-0046</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>If Allow Over Credit Limit is off, what status does an over-limit line have?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>KB-0046</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>How does Allow Over Credit Limit affect order line status?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>KB-0046</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>What does turning off Allow Over Credit Limit do to order lines?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>KB-0047</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>How do I update a line from Planned to Ordered?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>KB-0047</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>What tool changes a line's status to Ordered?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>KB-0047</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Who can change a line from Planned to Ordered?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>KB-0048</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Why is the Available to Ship Report different from the Ready quantity?</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>KB-0048</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>How come the Available to Ship and Ready quantities don't match?</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>KB-0048</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>What causes a mismatch between Available to Ship and Ready quantities?</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>KB-0049</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>What do I need to review before confirming product availability?</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>KB-0049</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Which things should I look at before saying something is available to ship?</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>KB-0049</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>What should I verify before telling a customer their order is available?</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>KB-0050</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Does the price update if I change the order quantity?</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>KB-0050</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Will the unit price change when I adjust the line quantity?</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>KB-0050</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>If I edit the quantity, do I need to check the price?</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>KB-0051</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Can I invoice a shipped line if it's on Invoice Hold?</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>KB-0051</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>What does Invoice Hold do for shipped order lines?</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>KB-0051</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Is it possible to edit or delete a shipped or invoiced line?</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F31" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
